--- a/phase5_1/input/inventory.xlsx
+++ b/phase5_1/input/inventory.xlsx
@@ -1,34 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\procurement\phase5_1\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+  <si>
+    <t>Transaction Date</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Item ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Ext. Cost</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>Digi-Key</t>
+  </si>
+  <si>
+    <t>DEMO-001</t>
+  </si>
+  <si>
+    <t>Joystick THB001P (108‑THB001P‑ND)</t>
+  </si>
+  <si>
+    <t>DEMO-002</t>
+  </si>
+  <si>
+    <t>Fuse 3.15A (5923‑5HT3.15‑R‑ND)</t>
+  </si>
+  <si>
+    <t>DEMO-003</t>
+  </si>
+  <si>
+    <t>Part 863‑1523‑2‑ND</t>
+  </si>
+  <si>
+    <t>DEMO-004</t>
+  </si>
+  <si>
+    <t>Sensor SHT40‑AD1B (1649‑…)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +114,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,238 +418,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Transaction Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Vendor Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Item ID</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Ext. Cost</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vendor A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ABC1234</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Resistor ABC1234 10K</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Vendor A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>XYZ9876</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Capacitor XYZ9876 10uF</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Vendor B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LMN5555</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Regulator LMN5555 5V</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Vendor B</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NC9999</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Custom Assembly NC9999</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>600</v>
-      </c>
-      <c r="F5" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Vendor C</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AAA1111</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Connector AAA1111</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>500</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Vendor C</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BBB2222</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Relay BBB2222</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>100</v>
-      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/phase5_1/input/inventory.xlsx
+++ b/phase5_1/input/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Transaction Date</t>
   </si>
@@ -72,13 +72,40 @@
     <t>DEMO-003</t>
   </si>
   <si>
-    <t>Part 863‑1523‑2‑ND</t>
-  </si>
-  <si>
     <t>DEMO-004</t>
   </si>
   <si>
-    <t>Sensor SHT40‑AD1B (1649‑…)</t>
+    <t>THERM NTC 10KOHM 3984K RING LUG</t>
+  </si>
+  <si>
+    <t>CONTACTR SS SPST-NO 35A 150-510V</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>Switching Voltage Regulators Buck Sw Reg</t>
+  </si>
+  <si>
+    <t>Circuit Breakers 508,DM,24VDC,CL,16A,ATX</t>
+  </si>
+  <si>
+    <t>584-LT1076HVIR#PBF</t>
+  </si>
+  <si>
+    <t>457-REX22DTA116E</t>
+  </si>
+  <si>
+    <t>571-10219128-02</t>
+  </si>
+  <si>
+    <t>Board Mount Temperature Sensors ESA PROBE-RTD PT1000 2000mm</t>
+  </si>
+  <si>
+    <t>225-DCM30V10L20S1PFB</t>
+  </si>
+  <si>
+    <t>Power Meters DC METER, 1000 V 300 A, ETH+RS485, MID</t>
   </si>
 </sst>
 </file>
@@ -114,9 +141,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +450,7 @@
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -508,7 +534,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>80</v>
@@ -528,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -544,16 +570,96 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>12.5</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>45</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>18</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>120</v>
+      </c>
+      <c r="F9">
+        <v>120</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
